--- a/outputs/shortlisted_candidates.xlsx
+++ b/outputs/shortlisted_candidates.xlsx
@@ -425,30 +425,30 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Candidate</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Experience</t>
@@ -461,66 +461,183 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Matched Skills</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Missing Skills</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Work Experience</t>
+          <t>Skill Match %</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Resume</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Similarity Score</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>resume_05_Sophia_Miller.pdf</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>sophia.miller@example.com</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>+1-555-0105</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>res2.txt</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>0.391</v>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>c, excel, java, rag</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.501</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>resume_04_Liam_Davis.pdf</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>liam.davis@example.com</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>+1-555-0104</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>res1.txt</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>0.367</v>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>c, excel, java, rag</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.489</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>resume_06_Ethan_Johnson.pdf</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ethan.johnson@example.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>+1-555-0106</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>c, excel, java, rag</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.409</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>resume_01_Emma_Wilson.pdf</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>emma.wilson@example.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>+1-555-0101</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>c, excel, java, rag</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.391</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>resume_03_Olivia_Brown.pdf</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>olivia.brown@example.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>+1-555-0103</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>c, excel, java, rag</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.388</v>
       </c>
     </row>
   </sheetData>
